--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -518,7 +518,7 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
 </t>
   </si>
   <si>
@@ -534,7 +534,7 @@
     <t>identityReliability</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-ident-reliability}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-ident-reliability}
 </t>
   </si>
   <si>
@@ -550,7 +550,7 @@
     <t>deathPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
 </t>
   </si>
   <si>
@@ -566,7 +566,7 @@
     <t>identityMethodCollection</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-identity-method-collection}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-identity-method-collection}
 </t>
   </si>
   <si>
@@ -582,7 +582,7 @@
     <t>birthdateUpdateIndicator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
 </t>
   </si>
   <si>
@@ -644,7 +644,7 @@
     <t>Patient.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
@@ -684,7 +684,7 @@
     <t>inseeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code}
 </t>
   </si>
   <si>
@@ -1539,7 +1539,7 @@
     <t>Patient.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
 </t>
   </si>
   <si>
@@ -1790,7 +1790,7 @@
     <t>birth-list-given-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name}
 </t>
   </si>
   <si>
@@ -1827,7 +1827,7 @@
     <t>Patient.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -2067,7 +2067,7 @@
     <t>contactIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
 </t>
   </si>
   <si>
@@ -2083,7 +2083,7 @@
     <t>comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
 </t>
   </si>
   <si>
@@ -2147,7 +2147,7 @@
     <t>The nature of the relationship. Rôle de la personne</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RolePerson.id</t>
@@ -2366,7 +2366,7 @@
     <t>The nature of the relationship. Relation de la personne</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelatedPerson.id</t>
@@ -2591,7 +2591,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
 </t>
   </si>
   <si>
@@ -2615,7 +2615,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -3008,7 +3008,7 @@
     <col min="8" max="8" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="142.73046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="144.640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6675" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6674" uniqueCount="856">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1856,7 +1856,7 @@
     <t>Patient.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
+    <t>male | female | unknown</t>
   </si>
   <si>
     <t>French patient's gender checked with the INSi teleservice | Genre du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs sont M ou F</t>
@@ -1868,10 +1868,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-gender-INS</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -2457,10 +2454,19 @@
     <t>Patient.contact.gender</t>
   </si>
   <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
     <t>Administrative Gender - the gender that the contact person is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
+  </si>
+  <si>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>NK1-15</t>
@@ -17197,11 +17203,9 @@
       <c r="X121" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y121" t="s" s="2">
+      <c r="Y121" s="2"/>
+      <c r="Z121" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>38</v>
@@ -17234,16 +17238,16 @@
         <v>59</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AL121" t="s" s="2">
+      <c r="AM121" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>38</v>
@@ -17251,10 +17255,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17277,19 +17281,19 @@
         <v>47</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M122" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>38</v>
@@ -17338,7 +17342,7 @@
         <v>38</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>36</v>
@@ -17353,27 +17357,27 @@
         <v>59</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AL122" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AL122" t="s" s="2">
+      <c r="AM122" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AM122" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>599</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17396,19 +17400,19 @@
         <v>47</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>38</v>
@@ -17457,7 +17461,7 @@
         <v>38</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>36</v>
@@ -17472,7 +17476,7 @@
         <v>59</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>66</v>
@@ -17481,7 +17485,7 @@
         <v>38</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>38</v>
@@ -17489,10 +17493,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17527,7 +17531,7 @@
         <v>203</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>38</v>
@@ -17576,7 +17580,7 @@
         <v>38</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>36</v>
@@ -17608,10 +17612,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17637,16 +17641,16 @@
         <v>351</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>38</v>
@@ -17674,11 +17678,11 @@
         <v>110</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="Z125" t="s" s="2">
-        <v>616</v>
-      </c>
       <c r="AA125" t="s" s="2">
         <v>38</v>
       </c>
@@ -17695,7 +17699,7 @@
         <v>38</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>36</v>
@@ -17710,16 +17714,16 @@
         <v>59</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>38</v>
@@ -17727,10 +17731,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17753,19 +17757,19 @@
         <v>38</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>38</v>
@@ -17814,7 +17818,7 @@
         <v>38</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>36</v>
@@ -17829,7 +17833,7 @@
         <v>59</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>66</v>
@@ -17838,7 +17842,7 @@
         <v>38</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>38</v>
@@ -17846,10 +17850,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17872,19 +17876,19 @@
         <v>38</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>38</v>
@@ -17933,7 +17937,7 @@
         <v>38</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>36</v>
@@ -17945,10 +17949,10 @@
         <v>58</v>
       </c>
       <c r="AJ127" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AK127" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>66</v>
@@ -17957,7 +17961,7 @@
         <v>38</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>38</v>
@@ -17965,10 +17969,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17991,19 +17995,19 @@
         <v>38</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>38</v>
@@ -18052,7 +18056,7 @@
         <v>38</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>36</v>
@@ -18064,10 +18068,10 @@
         <v>58</v>
       </c>
       <c r="AJ128" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AK128" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>66</v>
@@ -18084,10 +18088,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18199,10 +18203,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18314,13 +18318,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C131" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>38</v>
@@ -18342,13 +18346,13 @@
         <v>38</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18431,13 +18435,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C132" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>38</v>
@@ -18459,13 +18463,13 @@
         <v>38</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18548,14 +18552,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18577,10 +18581,10 @@
         <v>69</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>72</v>
@@ -18635,7 +18639,7 @@
         <v>38</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>36</v>
@@ -18667,10 +18671,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18696,16 +18700,16 @@
         <v>351</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O134" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>38</v>
@@ -18733,16 +18737,16 @@
         <v>110</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="Z134" t="s" s="2">
+      <c r="AA134" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB134" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
@@ -18752,7 +18756,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>36</v>
@@ -18767,7 +18771,7 @@
         <v>59</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>66</v>
@@ -18776,7 +18780,7 @@
         <v>38</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>38</v>
@@ -18784,13 +18788,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C135" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>38</v>
@@ -18815,16 +18819,16 @@
         <v>351</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M135" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O135" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>38</v>
@@ -18853,7 +18857,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>38</v>
@@ -18871,7 +18875,7 @@
         <v>38</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>36</v>
@@ -18886,7 +18890,7 @@
         <v>59</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>66</v>
@@ -18895,7 +18899,7 @@
         <v>38</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>38</v>
@@ -18903,10 +18907,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19018,10 +19022,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B137" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19135,10 +19139,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19164,16 +19168,16 @@
         <v>106</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="N138" t="s" s="2">
+      <c r="O138" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>38</v>
@@ -19222,7 +19226,7 @@
         <v>38</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>36</v>
@@ -19237,16 +19241,16 @@
         <v>59</v>
       </c>
       <c r="AK138" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN138" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>38</v>
@@ -19254,10 +19258,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B139" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19369,10 +19373,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B140" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19486,10 +19490,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19515,16 +19519,16 @@
         <v>90</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="N141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>38</v>
@@ -19534,46 +19538,46 @@
         <v>38</v>
       </c>
       <c r="S141" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF141" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>36</v>
@@ -19588,16 +19592,16 @@
         <v>59</v>
       </c>
       <c r="AK141" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN141" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>38</v>
@@ -19605,10 +19609,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19634,13 +19638,13 @@
         <v>62</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19690,7 +19694,7 @@
         <v>38</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>36</v>
@@ -19705,16 +19709,16 @@
         <v>59</v>
       </c>
       <c r="AK142" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>38</v>
@@ -19722,10 +19726,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19751,16 +19755,16 @@
         <v>130</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>253</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>38</v>
@@ -19809,7 +19813,7 @@
         <v>38</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>36</v>
@@ -19824,16 +19828,16 @@
         <v>59</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>38</v>
@@ -19841,10 +19845,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B144" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19870,16 +19874,16 @@
         <v>62</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>253</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>38</v>
@@ -19928,7 +19932,7 @@
         <v>38</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>36</v>
@@ -19943,16 +19947,16 @@
         <v>59</v>
       </c>
       <c r="AK144" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN144" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>38</v>
@@ -19960,10 +19964,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B145" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19989,16 +19993,16 @@
         <v>470</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>38</v>
@@ -20047,7 +20051,7 @@
         <v>38</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>36</v>
@@ -20062,16 +20066,16 @@
         <v>59</v>
       </c>
       <c r="AK145" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>38</v>
@@ -20079,10 +20083,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="B146" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20108,16 +20112,16 @@
         <v>62</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>38</v>
@@ -20166,7 +20170,7 @@
         <v>38</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>36</v>
@@ -20181,16 +20185,16 @@
         <v>59</v>
       </c>
       <c r="AK146" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>38</v>
@@ -20198,13 +20202,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C147" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>38</v>
@@ -20229,16 +20233,16 @@
         <v>351</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M147" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O147" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>38</v>
@@ -20267,7 +20271,7 @@
       </c>
       <c r="Y147" s="2"/>
       <c r="Z147" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>38</v>
@@ -20285,7 +20289,7 @@
         <v>38</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>36</v>
@@ -20300,7 +20304,7 @@
         <v>59</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>66</v>
@@ -20309,7 +20313,7 @@
         <v>38</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>38</v>
@@ -20317,10 +20321,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20432,10 +20436,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20549,10 +20553,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20578,16 +20582,16 @@
         <v>106</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>38</v>
@@ -20636,7 +20640,7 @@
         <v>38</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>36</v>
@@ -20651,16 +20655,16 @@
         <v>59</v>
       </c>
       <c r="AK150" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN150" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>38</v>
@@ -20668,10 +20672,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20783,10 +20787,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20900,10 +20904,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20929,16 +20933,16 @@
         <v>90</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>38</v>
@@ -20948,7 +20952,7 @@
         <v>38</v>
       </c>
       <c r="S153" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="T153" t="s" s="2">
         <v>38</v>
@@ -20987,7 +20991,7 @@
         <v>38</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>36</v>
@@ -21002,16 +21006,16 @@
         <v>59</v>
       </c>
       <c r="AK153" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN153" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>38</v>
@@ -21019,10 +21023,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21048,13 +21052,13 @@
         <v>62</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21104,7 +21108,7 @@
         <v>38</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>36</v>
@@ -21119,16 +21123,16 @@
         <v>59</v>
       </c>
       <c r="AK154" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>38</v>
@@ -21136,10 +21140,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21165,16 +21169,16 @@
         <v>130</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>253</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>38</v>
@@ -21223,7 +21227,7 @@
         <v>38</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>36</v>
@@ -21238,16 +21242,16 @@
         <v>59</v>
       </c>
       <c r="AK155" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN155" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>38</v>
@@ -21255,10 +21259,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21284,16 +21288,16 @@
         <v>62</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>253</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>38</v>
@@ -21342,7 +21346,7 @@
         <v>38</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>36</v>
@@ -21357,16 +21361,16 @@
         <v>59</v>
       </c>
       <c r="AK156" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN156" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>38</v>
@@ -21374,10 +21378,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21403,16 +21407,16 @@
         <v>470</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>38</v>
@@ -21461,7 +21465,7 @@
         <v>38</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>36</v>
@@ -21476,16 +21480,16 @@
         <v>59</v>
       </c>
       <c r="AK157" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN157" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>38</v>
@@ -21493,10 +21497,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21522,16 +21526,16 @@
         <v>62</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="N158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>38</v>
@@ -21580,7 +21584,7 @@
         <v>38</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>36</v>
@@ -21595,16 +21599,16 @@
         <v>59</v>
       </c>
       <c r="AK158" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN158" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>38</v>
@@ -21612,10 +21616,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21641,16 +21645,16 @@
         <v>479</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>761</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>38</v>
@@ -21699,7 +21703,7 @@
         <v>38</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>36</v>
@@ -21714,16 +21718,16 @@
         <v>59</v>
       </c>
       <c r="AK159" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN159" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>38</v>
@@ -21731,10 +21735,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21766,7 +21770,7 @@
         <v>575</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="O160" t="s" s="2">
         <v>577</v>
@@ -21818,7 +21822,7 @@
         <v>38</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>36</v>
@@ -21850,10 +21854,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21876,19 +21880,19 @@
         <v>38</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>203</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>38</v>
@@ -21937,7 +21941,7 @@
         <v>38</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>36</v>
@@ -21952,7 +21956,7 @@
         <v>59</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>66</v>
@@ -21961,7 +21965,7 @@
         <v>38</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>38</v>
@@ -21969,10 +21973,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21998,7 +22002,7 @@
         <v>130</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>582</v>
+        <v>776</v>
       </c>
       <c r="M162" t="s" s="2">
         <v>777</v>
@@ -22035,10 +22039,10 @@
         <v>223</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>586</v>
+        <v>779</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>587</v>
+        <v>780</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>38</v>
@@ -22056,7 +22060,7 @@
         <v>38</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>36</v>
@@ -22071,7 +22075,7 @@
         <v>59</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>66</v>
@@ -22080,7 +22084,7 @@
         <v>38</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>38</v>
@@ -22088,10 +22092,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22117,16 +22121,16 @@
         <v>389</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>38</v>
@@ -22175,7 +22179,7 @@
         <v>38</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>36</v>
@@ -22184,13 +22188,13 @@
         <v>46</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>394</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>66</v>
@@ -22199,7 +22203,7 @@
         <v>38</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>38</v>
@@ -22207,10 +22211,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22236,10 +22240,10 @@
         <v>304</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>307</v>
@@ -22292,7 +22296,7 @@
         <v>38</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>36</v>
@@ -22307,7 +22311,7 @@
         <v>311</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>66</v>
@@ -22316,7 +22320,7 @@
         <v>38</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>38</v>
@@ -22324,10 +22328,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22350,19 +22354,19 @@
         <v>38</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>38</v>
@@ -22411,7 +22415,7 @@
         <v>38</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>36</v>
@@ -22426,10 +22430,10 @@
         <v>59</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>38</v>
@@ -22443,10 +22447,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22558,10 +22562,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22675,14 +22679,14 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -22704,10 +22708,10 @@
         <v>69</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>72</v>
@@ -22762,7 +22766,7 @@
         <v>38</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>36</v>
@@ -22794,10 +22798,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22823,16 +22827,16 @@
         <v>351</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>38</v>
@@ -22881,7 +22885,7 @@
         <v>38</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>46</v>
@@ -22896,16 +22900,16 @@
         <v>59</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>38</v>
@@ -22913,10 +22917,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22942,16 +22946,16 @@
         <v>470</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>38</v>
@@ -23000,7 +23004,7 @@
         <v>38</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>36</v>
@@ -23015,16 +23019,16 @@
         <v>59</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>38</v>
@@ -23032,14 +23036,14 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -23058,16 +23062,16 @@
         <v>38</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -23117,7 +23121,7 @@
         <v>38</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>36</v>
@@ -23132,7 +23136,7 @@
         <v>394</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>66</v>
@@ -23141,7 +23145,7 @@
         <v>38</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>38</v>
@@ -23149,10 +23153,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23175,19 +23179,19 @@
         <v>47</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>38</v>
@@ -23236,7 +23240,7 @@
         <v>38</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>36</v>
@@ -23251,10 +23255,10 @@
         <v>394</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>38</v>
@@ -23268,10 +23272,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23294,19 +23298,19 @@
         <v>47</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>38</v>
@@ -23355,7 +23359,7 @@
         <v>38</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>36</v>
@@ -23370,7 +23374,7 @@
         <v>59</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>66</v>
@@ -23387,10 +23391,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23502,10 +23506,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23619,14 +23623,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -23648,10 +23652,10 @@
         <v>69</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>72</v>
@@ -23706,7 +23710,7 @@
         <v>38</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>36</v>
@@ -23738,10 +23742,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23764,16 +23768,16 @@
         <v>47</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23823,7 +23827,7 @@
         <v>38</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>46</v>
@@ -23847,7 +23851,7 @@
         <v>38</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>38</v>
@@ -23855,10 +23859,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23884,10 +23888,10 @@
         <v>130</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>253</v>
@@ -23919,28 +23923,28 @@
         <v>223</v>
       </c>
       <c r="Y178" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF178" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>849</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>46</v>
@@ -23955,7 +23959,7 @@
         <v>59</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>66</v>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1250,7 +1250,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
     &lt;display value="INS calculé"/&gt;
   &lt;/coding&gt;
@@ -1411,14 +1411,14 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
     &lt;display value="Identifiant au dossier pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-core-patient-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.system</t>
@@ -1552,7 +1552,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-NIR"/&gt;
     &lt;display value="NIR"/&gt;
   &lt;/coding&gt;
@@ -1603,7 +1603,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-NIA"/&gt;
     &lt;display value="NIA"/&gt;
   &lt;/coding&gt;
@@ -3153,7 +3153,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.94140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.37109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1400,7 +1400,7 @@
   &lt;coding&gt;
     &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
-    &lt;display value="INS calculé"/&gt;
+    &lt;display value="Identifiant National de Santé Calculé"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1561,7 +1561,7 @@
   &lt;coding&gt;
     &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
-    &lt;display value="Identifiant au dossier pharmaceutique"/&gt;
+    &lt;display value="Identifiant du patient au Dossier Pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FrPatient appliqué à l'INS avec identité validée. Pour plus d'informations sur le contexte du patient INS, consultez le référentiel national d'identitovigilance (RNIV) et la documentation du référentiel INS de l'ANS .</t>
+    <t>Profil FRCorePatientProfile appliqué à l'INS avec identité validée, permettant d'indiquer les contraintes fortes nécessaires pour modéliser un patient avec une INS validée. Une ressource conforme au profil FRCorePatientINSProfile sera également conforme au profil FRCorePatientProfile grâce au principe d'héritage, il n'est donc pas nécessaire d'avoir une instance de chaque profil pour un même patient. Pour plus d'informations sur le contexte du patient INS, consultez le référentiel national d'identitovigilance (RNIV) et la documentation du référentiel INS de l'ANS .</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1292,7 +1292,7 @@
 </t>
   </si>
   <si>
-    <t>National Health Identifier | Identifiant national de santé</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -12425,7 +12425,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -14541,7 +14541,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>81</v>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6912" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6911" uniqueCount="862">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2219,10 +2219,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>The domestic partnership status of a person.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -21069,11 +21066,9 @@
       <c r="X154" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y154" t="s" s="2">
+      <c r="Y154" s="2"/>
+      <c r="Z154" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>81</v>
@@ -21106,16 +21101,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AL154" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AL154" t="s" s="2">
+      <c r="AM154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21123,10 +21118,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21149,19 +21144,19 @@
         <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21210,7 +21205,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21225,7 +21220,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>109</v>
@@ -21234,7 +21229,7 @@
         <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>81</v>
@@ -21242,10 +21237,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21268,19 +21263,19 @@
         <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21329,7 +21324,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21341,10 +21336,10 @@
         <v>101</v>
       </c>
       <c r="AJ156" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AK156" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>109</v>
@@ -21353,7 +21348,7 @@
         <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>81</v>
@@ -21361,10 +21356,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21387,19 +21382,19 @@
         <v>81</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21448,7 +21443,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21460,10 +21455,10 @@
         <v>101</v>
       </c>
       <c r="AJ157" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="AK157" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>109</v>
@@ -21480,10 +21475,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21595,10 +21590,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21712,13 +21707,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C160" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>81</v>
@@ -21740,13 +21735,13 @@
         <v>81</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21829,13 +21824,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C161" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>81</v>
@@ -21857,13 +21852,13 @@
         <v>81</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21946,14 +21941,14 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21975,10 +21970,10 @@
         <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>115</v>
@@ -22033,7 +22028,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22065,10 +22060,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22094,16 +22089,16 @@
         <v>440</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>700</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22131,16 +22126,16 @@
         <v>153</v>
       </c>
       <c r="Y163" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="Z163" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="Z163" t="s" s="2">
+      <c r="AA163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB163" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="AC163" s="2"/>
       <c r="AD163" t="s" s="2">
@@ -22150,7 +22145,7 @@
         <v>118</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22165,7 +22160,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>109</v>
@@ -22174,7 +22169,7 @@
         <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
@@ -22182,13 +22177,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>81</v>
@@ -22213,16 +22208,16 @@
         <v>440</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>700</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22251,7 +22246,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>81</v>
@@ -22269,7 +22264,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22284,7 +22279,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>109</v>
@@ -22293,7 +22288,7 @@
         <v>81</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
@@ -22301,13 +22296,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C165" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
@@ -22332,16 +22327,16 @@
         <v>440</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>700</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22370,7 +22365,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -22388,7 +22383,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22403,7 +22398,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>109</v>
@@ -22412,7 +22407,7 @@
         <v>81</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>81</v>
@@ -22420,10 +22415,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22449,16 +22444,16 @@
         <v>568</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22507,7 +22502,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22522,16 +22517,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>81</v>
@@ -22539,10 +22534,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22574,7 +22569,7 @@
         <v>664</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O167" t="s" s="2">
         <v>666</v>
@@ -22626,7 +22621,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22658,10 +22653,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22684,19 +22679,19 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>294</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22745,7 +22740,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22760,7 +22755,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>109</v>
@@ -22769,7 +22764,7 @@
         <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>81</v>
@@ -22777,10 +22772,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22806,16 +22801,16 @@
         <v>173</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>342</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22843,11 +22838,11 @@
         <v>264</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="Z169" t="s" s="2">
-        <v>787</v>
-      </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
       </c>
@@ -22864,7 +22859,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22888,7 +22883,7 @@
         <v>81</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22896,10 +22891,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22925,16 +22920,16 @@
         <v>478</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
@@ -22983,7 +22978,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22992,13 +22987,13 @@
         <v>89</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>483</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>109</v>
@@ -23007,7 +23002,7 @@
         <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>81</v>
@@ -23015,10 +23010,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23044,10 +23039,10 @@
         <v>393</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>396</v>
@@ -23100,7 +23095,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -23115,7 +23110,7 @@
         <v>400</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>109</v>
@@ -23124,7 +23119,7 @@
         <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>81</v>
@@ -23132,10 +23127,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23158,19 +23153,19 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>803</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -23219,7 +23214,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23234,10 +23229,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AL172" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>81</v>
@@ -23251,10 +23246,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23366,10 +23361,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23483,14 +23478,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23512,10 +23507,10 @@
         <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>115</v>
@@ -23570,7 +23565,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23602,10 +23597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23631,16 +23626,16 @@
         <v>440</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="N176" t="s" s="2">
+      <c r="O176" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23689,7 +23684,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>89</v>
@@ -23704,16 +23699,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AL176" t="s" s="2">
         <v>817</v>
       </c>
-      <c r="AL176" t="s" s="2">
+      <c r="AM176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN176" t="s" s="2">
         <v>818</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>819</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>81</v>
@@ -23721,10 +23716,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23750,16 +23745,16 @@
         <v>559</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>81</v>
@@ -23808,7 +23803,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23823,16 +23818,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AL177" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="AL177" t="s" s="2">
+      <c r="AM177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN177" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23840,14 +23835,14 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23866,16 +23861,16 @@
         <v>81</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23925,7 +23920,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23940,7 +23935,7 @@
         <v>483</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>109</v>
@@ -23949,7 +23944,7 @@
         <v>81</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>81</v>
@@ -23957,10 +23952,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23983,19 +23978,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>839</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
@@ -24044,7 +24039,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24059,10 +24054,10 @@
         <v>483</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>81</v>
@@ -24076,10 +24071,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24102,19 +24097,19 @@
         <v>90</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="N180" t="s" s="2">
+      <c r="O180" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -24163,7 +24158,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24178,7 +24173,7 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>109</v>
@@ -24195,10 +24190,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24310,10 +24305,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24427,14 +24422,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24456,10 +24451,10 @@
         <v>112</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>115</v>
@@ -24514,7 +24509,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24546,10 +24541,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24572,16 +24567,16 @@
         <v>90</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="M184" t="s" s="2">
+      <c r="N184" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24631,7 +24626,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>89</v>
@@ -24655,7 +24650,7 @@
         <v>81</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>81</v>
@@ -24663,10 +24658,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24692,10 +24687,10 @@
         <v>173</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="N185" t="s" s="2">
         <v>342</v>
@@ -24727,11 +24722,11 @@
         <v>264</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="Z185" t="s" s="2">
-        <v>861</v>
-      </c>
       <c r="AA185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24748,7 +24743,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24763,7 +24758,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>109</v>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6911" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6911" uniqueCount="861">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1536,10 +1536,7 @@
     <t>NDP</t>
   </si>
   <si>
-    <t>French pharmaceutical Record Identifier | Numéro de Dossier Pharmaceutique français</t>
-  </si>
-  <si>
-    <t>Pharmaceutical Record Identifier | Numéro de Dossier Pharmaceutique</t>
+    <t>French pharmaceutical Record Identifier | Numéro de Dossier Pharmaceutique français. Celui-ci est unique.</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.id</t>
@@ -12422,7 +12419,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -12440,7 +12437,7 @@
         <v>488</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>489</v>
+        <v>411</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
@@ -12525,7 +12522,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>424</v>
@@ -12640,7 +12637,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>426</v>
@@ -12757,7 +12754,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>428</v>
@@ -12876,7 +12873,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>439</v>
@@ -12908,7 +12905,7 @@
         <v>441</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>442</v>
@@ -12924,7 +12921,7 @@
         <v>81</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>81</v>
@@ -12943,7 +12940,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -12993,7 +12990,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>450</v>
@@ -13041,7 +13038,7 @@
         <v>81</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>456</v>
@@ -13112,7 +13109,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>461</v>
@@ -13229,7 +13226,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>470</v>
@@ -13346,7 +13343,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>477</v>
@@ -13463,13 +13460,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>81</v>
@@ -13494,10 +13491,10 @@
         <v>409</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
@@ -13582,7 +13579,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>424</v>
@@ -13697,7 +13694,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>426</v>
@@ -13814,7 +13811,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>428</v>
@@ -13862,7 +13859,7 @@
         <v>81</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>81</v>
@@ -13933,7 +13930,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>439</v>
@@ -13965,7 +13962,7 @@
         <v>441</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>442</v>
@@ -13981,7 +13978,7 @@
         <v>81</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>81</v>
@@ -14052,7 +14049,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>450</v>
@@ -14171,7 +14168,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>461</v>
@@ -14288,7 +14285,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>470</v>
@@ -14405,7 +14402,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>477</v>
@@ -14522,13 +14519,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>81</v>
@@ -14553,10 +14550,10 @@
         <v>409</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -14641,7 +14638,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>424</v>
@@ -14756,7 +14753,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>426</v>
@@ -14873,7 +14870,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>428</v>
@@ -14992,7 +14989,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>439</v>
@@ -15024,7 +15021,7 @@
         <v>441</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>442</v>
@@ -15040,7 +15037,7 @@
         <v>81</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>81</v>
@@ -15111,7 +15108,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>450</v>
@@ -15230,7 +15227,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>461</v>
@@ -15347,7 +15344,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>470</v>
@@ -15464,7 +15461,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>477</v>
@@ -15581,13 +15578,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
@@ -15612,10 +15609,10 @@
         <v>409</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -15700,7 +15697,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>424</v>
@@ -15815,7 +15812,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>426</v>
@@ -15932,7 +15929,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>428</v>
@@ -15980,7 +15977,7 @@
         <v>81</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>81</v>
@@ -16051,7 +16048,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>439</v>
@@ -16083,7 +16080,7 @@
         <v>441</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>442</v>
@@ -16099,7 +16096,7 @@
         <v>81</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>81</v>
@@ -16170,7 +16167,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>450</v>
@@ -16199,7 +16196,7 @@
         <v>133</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>452</v>
@@ -16218,7 +16215,7 @@
         <v>81</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>456</v>
@@ -16289,7 +16286,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>461</v>
@@ -16406,7 +16403,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>470</v>
@@ -16523,7 +16520,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>477</v>
@@ -16640,13 +16637,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
@@ -16671,10 +16668,10 @@
         <v>409</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
@@ -16759,7 +16756,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>424</v>
@@ -16874,7 +16871,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>426</v>
@@ -16991,7 +16988,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>428</v>
@@ -17039,7 +17036,7 @@
         <v>81</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>81</v>
@@ -17110,7 +17107,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>439</v>
@@ -17142,7 +17139,7 @@
         <v>441</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>442</v>
@@ -17158,7 +17155,7 @@
         <v>81</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>81</v>
@@ -17229,7 +17226,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>450</v>
@@ -17258,7 +17255,7 @@
         <v>133</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>452</v>
@@ -17277,7 +17274,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>456</v>
@@ -17348,7 +17345,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>461</v>
@@ -17465,7 +17462,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>470</v>
@@ -17582,7 +17579,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>477</v>
@@ -17699,10 +17696,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17725,26 +17722,26 @@
         <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="O126" t="s" s="2">
+      <c r="P126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q126" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="P126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q126" t="s" s="2">
-        <v>564</v>
-      </c>
       <c r="R126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17788,7 +17785,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17803,13 +17800,13 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
@@ -17820,10 +17817,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17846,19 +17843,19 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17895,7 +17892,7 @@
         <v>81</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AC127" s="2"/>
       <c r="AD127" t="s" s="2">
@@ -17905,7 +17902,7 @@
         <v>118</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17920,16 +17917,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AL127" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AL127" t="s" s="2">
+      <c r="AM127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -17937,13 +17934,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C128" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>81</v>
@@ -17965,19 +17962,19 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M128" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="N128" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O128" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -18026,7 +18023,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -18041,16 +18038,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AL128" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AL128" t="s" s="2">
+      <c r="AM128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>81</v>
@@ -18058,10 +18055,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18173,10 +18170,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18290,10 +18287,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18319,16 +18316,16 @@
         <v>173</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -18338,7 +18335,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -18356,28 +18353,28 @@
         <v>264</v>
       </c>
       <c r="Y131" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z131" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z131" t="s" s="2">
+      <c r="AA131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF131" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18401,7 +18398,7 @@
         <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>81</v>
@@ -18409,10 +18406,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B132" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18438,13 +18435,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>333</v>
@@ -18496,7 +18493,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18520,7 +18517,7 @@
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18528,14 +18525,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18557,13 +18554,13 @@
         <v>105</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18613,7 +18610,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18628,16 +18625,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>81</v>
@@ -18645,14 +18642,14 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18674,13 +18671,13 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18730,7 +18727,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18745,16 +18742,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>81</v>
@@ -18762,10 +18759,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18791,10 +18788,10 @@
         <v>105</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>342</v>
@@ -18847,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18862,16 +18859,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN135" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>81</v>
@@ -18879,10 +18876,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18908,10 +18905,10 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>342</v>
@@ -18964,7 +18961,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18979,16 +18976,16 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN136" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>81</v>
@@ -18996,10 +18993,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B137" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19025,16 +19022,16 @@
         <v>393</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>396</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -19083,7 +19080,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19107,7 +19104,7 @@
         <v>81</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>81</v>
@@ -19115,13 +19112,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>81</v>
@@ -19143,19 +19140,19 @@
         <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M138" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="N138" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O138" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -19204,7 +19201,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19219,16 +19216,16 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AL138" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AL138" t="s" s="2">
+      <c r="AM138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN138" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>81</v>
@@ -19236,10 +19233,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19351,10 +19348,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19466,13 +19463,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C141" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>81</v>
@@ -19494,13 +19491,13 @@
         <v>81</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19583,10 +19580,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19612,16 +19609,16 @@
         <v>173</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
@@ -19631,7 +19628,7 @@
         <v>81</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>81</v>
@@ -19649,28 +19646,28 @@
         <v>264</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z142" t="s" s="2">
+      <c r="AA142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF142" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19694,7 +19691,7 @@
         <v>81</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>81</v>
@@ -19702,10 +19699,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19731,13 +19728,13 @@
         <v>105</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="O143" t="s" s="2">
         <v>333</v>
@@ -19789,7 +19786,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19813,7 +19810,7 @@
         <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>81</v>
@@ -19821,14 +19818,14 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19850,13 +19847,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19906,7 +19903,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19921,16 +19918,16 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN144" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>81</v>
@@ -19938,14 +19935,14 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19967,13 +19964,13 @@
         <v>105</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M145" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20023,7 +20020,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20038,16 +20035,16 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>81</v>
@@ -20055,10 +20052,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20084,10 +20081,10 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>342</v>
@@ -20140,7 +20137,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20155,16 +20152,16 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>81</v>
@@ -20172,10 +20169,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20201,10 +20198,10 @@
         <v>105</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>342</v>
@@ -20257,7 +20254,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20272,16 +20269,16 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>81</v>
@@ -20289,10 +20286,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20318,16 +20315,16 @@
         <v>393</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>396</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20376,7 +20373,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20400,7 +20397,7 @@
         <v>81</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>81</v>
@@ -20408,10 +20405,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20434,19 +20431,19 @@
         <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
@@ -20495,7 +20492,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20507,19 +20504,19 @@
         <v>101</v>
       </c>
       <c r="AJ149" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AK149" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="AK149" t="s" s="2">
+      <c r="AL149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN149" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>81</v>
@@ -20527,10 +20524,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20556,16 +20553,16 @@
         <v>173</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20594,7 +20591,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>81</v>
@@ -20612,7 +20609,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20627,16 +20624,16 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AL150" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="AL150" t="s" s="2">
+      <c r="AM150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN150" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>81</v>
@@ -20644,10 +20641,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20673,16 +20670,16 @@
         <v>241</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="M151" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>81</v>
@@ -20731,7 +20728,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20746,27 +20743,27 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AL151" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="AL151" t="s" s="2">
+      <c r="AM151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN151" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="AM151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN151" t="s" s="2">
+      <c r="AO151" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>686</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20789,19 +20786,19 @@
         <v>90</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="N152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -20850,7 +20847,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20865,7 +20862,7 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>109</v>
@@ -20874,7 +20871,7 @@
         <v>81</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>81</v>
@@ -20882,10 +20879,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20920,7 +20917,7 @@
         <v>294</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -20969,7 +20966,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21001,10 +20998,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21030,16 +21027,16 @@
         <v>440</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
@@ -21068,7 +21065,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>81</v>
@@ -21086,7 +21083,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21101,16 +21098,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AL154" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="AL154" t="s" s="2">
+      <c r="AM154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21118,10 +21115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21144,19 +21141,19 @@
         <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21205,7 +21202,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21220,7 +21217,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>109</v>
@@ -21229,7 +21226,7 @@
         <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>81</v>
@@ -21237,10 +21234,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21263,19 +21260,19 @@
         <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21324,7 +21321,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21336,10 +21333,10 @@
         <v>101</v>
       </c>
       <c r="AJ156" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AK156" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>109</v>
@@ -21348,7 +21345,7 @@
         <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>81</v>
@@ -21356,10 +21353,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21382,19 +21379,19 @@
         <v>81</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21443,7 +21440,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21455,10 +21452,10 @@
         <v>101</v>
       </c>
       <c r="AJ157" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AK157" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>109</v>
@@ -21475,10 +21472,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21590,10 +21587,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21707,13 +21704,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C160" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>81</v>
@@ -21735,13 +21732,13 @@
         <v>81</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21824,13 +21821,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C161" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>81</v>
@@ -21852,13 +21849,13 @@
         <v>81</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21941,14 +21938,14 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21970,10 +21967,10 @@
         <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>115</v>
@@ -22028,7 +22025,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22060,10 +22057,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22089,16 +22086,16 @@
         <v>440</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O163" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22126,16 +22123,16 @@
         <v>153</v>
       </c>
       <c r="Y163" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="Z163" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="Z163" t="s" s="2">
+      <c r="AA163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB163" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="AC163" s="2"/>
       <c r="AD163" t="s" s="2">
@@ -22145,7 +22142,7 @@
         <v>118</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22160,7 +22157,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>109</v>
@@ -22169,7 +22166,7 @@
         <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
@@ -22177,13 +22174,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>81</v>
@@ -22208,16 +22205,16 @@
         <v>440</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="M164" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O164" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22246,7 +22243,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>81</v>
@@ -22264,7 +22261,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22279,7 +22276,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>109</v>
@@ -22288,7 +22285,7 @@
         <v>81</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
@@ -22296,13 +22293,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="C165" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
@@ -22327,16 +22324,16 @@
         <v>440</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="M165" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O165" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22365,7 +22362,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -22383,7 +22380,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22398,7 +22395,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>109</v>
@@ -22407,7 +22404,7 @@
         <v>81</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>81</v>
@@ -22415,10 +22412,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22441,19 +22438,19 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22502,7 +22499,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22517,16 +22514,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>81</v>
@@ -22534,10 +22531,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22560,19 +22557,19 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L167" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L167" t="s" s="2">
+      <c r="M167" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M167" t="s" s="2">
-        <v>664</v>
-      </c>
       <c r="N167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>81</v>
@@ -22621,7 +22618,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22633,19 +22630,19 @@
         <v>101</v>
       </c>
       <c r="AJ167" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AK167" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="AK167" t="s" s="2">
+      <c r="AL167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN167" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>81</v>
@@ -22653,10 +22650,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22679,19 +22676,19 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>294</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22740,7 +22737,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22755,7 +22752,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>109</v>
@@ -22764,7 +22761,7 @@
         <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>81</v>
@@ -22772,10 +22769,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22801,16 +22798,16 @@
         <v>173</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>342</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22838,11 +22835,11 @@
         <v>264</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="Z169" t="s" s="2">
-        <v>786</v>
-      </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
       </c>
@@ -22859,7 +22856,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22874,7 +22871,7 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>109</v>
@@ -22883,7 +22880,7 @@
         <v>81</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22891,10 +22888,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22920,16 +22917,16 @@
         <v>478</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>789</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
@@ -22978,7 +22975,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22987,13 +22984,13 @@
         <v>89</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>483</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>109</v>
@@ -23002,7 +22999,7 @@
         <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>81</v>
@@ -23010,10 +23007,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23039,10 +23036,10 @@
         <v>393</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>396</v>
@@ -23095,7 +23092,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -23110,7 +23107,7 @@
         <v>400</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>109</v>
@@ -23119,7 +23116,7 @@
         <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>81</v>
@@ -23127,10 +23124,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23153,19 +23150,19 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>802</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>803</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>804</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>805</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -23214,7 +23211,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23229,10 +23226,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="AL172" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>81</v>
@@ -23246,10 +23243,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23361,10 +23358,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23478,14 +23475,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23507,10 +23504,10 @@
         <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>115</v>
@@ -23565,7 +23562,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23597,10 +23594,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23626,16 +23623,16 @@
         <v>440</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>812</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="N176" t="s" s="2">
+      <c r="O176" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23684,7 +23681,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>89</v>
@@ -23699,16 +23696,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AL176" t="s" s="2">
         <v>816</v>
       </c>
-      <c r="AL176" t="s" s="2">
+      <c r="AM176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN176" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>81</v>
@@ -23716,10 +23713,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23742,19 +23739,19 @@
         <v>81</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>81</v>
@@ -23803,7 +23800,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23818,16 +23815,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AL177" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="AL177" t="s" s="2">
+      <c r="AM177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN177" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23835,14 +23832,14 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23861,16 +23858,16 @@
         <v>81</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>829</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23920,7 +23917,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23935,7 +23932,7 @@
         <v>483</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>109</v>
@@ -23944,7 +23941,7 @@
         <v>81</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>81</v>
@@ -23952,10 +23949,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23978,19 +23975,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
@@ -24039,7 +24036,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24054,10 +24051,10 @@
         <v>483</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>81</v>
@@ -24071,10 +24068,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24097,19 +24094,19 @@
         <v>90</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>843</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="N180" t="s" s="2">
+      <c r="O180" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -24158,7 +24155,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24173,7 +24170,7 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>109</v>
@@ -24190,10 +24187,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24305,10 +24302,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24422,14 +24419,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24451,10 +24448,10 @@
         <v>112</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>115</v>
@@ -24509,7 +24506,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24541,10 +24538,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24567,16 +24564,16 @@
         <v>90</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>852</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="M184" t="s" s="2">
+      <c r="N184" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24626,7 +24623,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>89</v>
@@ -24650,7 +24647,7 @@
         <v>81</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>81</v>
@@ -24658,10 +24655,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24687,10 +24684,10 @@
         <v>173</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="N185" t="s" s="2">
         <v>342</v>
@@ -24722,11 +24719,11 @@
         <v>264</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>859</v>
       </c>
-      <c r="Z185" t="s" s="2">
-        <v>860</v>
-      </c>
       <c r="AA185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24743,7 +24740,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24758,7 +24755,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>109</v>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T10:12:17+00:00</t>
+    <t>2024-02-05T11:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,14 +647,14 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
 </t>
   </si>
   <si>
-    <t>FR Core Patient Nationalité</t>
-  </si>
-  <si>
-    <t>Nationalité du patient</t>
+    <t>Nationality</t>
+  </si>
+  <si>
+    <t>The nationality of the patient.</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability</t>
@@ -736,7 +736,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-identity-method-collection</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-method-collection</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -786,12 +786,12 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-fiabilite-identite"/&gt;
+  &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-fiabilite-identite"/&gt;
   &lt;code value="VALI"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-identity-reliability</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:validationDate</t>
@@ -1398,7 +1398,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
     &lt;display value="Identifiant National de Santé Calculé"/&gt;
   &lt;/coding&gt;
@@ -1556,14 +1556,14 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
     &lt;display value="Identifiant du patient au Dossier Pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.system</t>
@@ -1697,7 +1697,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INS-NIR"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1747,7 +1747,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INS-NIA"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2134,7 +2134,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-gender-INS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender-INS</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -2403,7 +2403,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelatedPerson</t>
@@ -2415,7 +2415,7 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -3054,7 +3054,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.4453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T11:48:42+00:00</t>
+    <t>2024-02-12T13:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6911" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7248" uniqueCount="870">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:27:08+00:00</t>
+    <t>2024-02-12T14:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1320,31 +1320,28 @@
     <t>PID-3</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C</t>
-  </si>
-  <si>
-    <t>INS-C</t>
-  </si>
-  <si>
-    <t>An identifier for this patient</t>
-  </si>
-  <si>
-    <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
-  </si>
-  <si>
-    <t>Patient.identifier:INS-C.id</t>
+    <t>Patient.identifier:NSS</t>
+  </si>
+  <si>
+    <t>NSS</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.id</t>
   </si>
   <si>
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.extension</t>
+    <t>Patient.identifier:NSS.extension</t>
   </si>
   <si>
     <t>Patient.identifier.extension</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.use</t>
+    <t>Patient.identifier:NSS.use</t>
   </si>
   <si>
     <t>Patient.identifier.use</t>
@@ -1362,7 +1359,7 @@
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
-    <t>secondary</t>
+    <t>official</t>
   </si>
   <si>
     <t>Identifies the purpose for this identifier, if known .</t>
@@ -1377,7 +1374,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.type</t>
+    <t>Patient.identifier:NSS.type</t>
   </si>
   <si>
     <t>Patient.identifier.type</t>
@@ -1390,10 +1387,170 @@
     <t>Description of identifier</t>
   </si>
   <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="NH"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.system</t>
+  </si>
+  <si>
+    <t>Patient.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.8</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier.period</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C</t>
+  </si>
+  <si>
+    <t>INS-C</t>
+  </si>
+  <si>
+    <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.use</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1405,131 +1562,21 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.system</t>
   </si>
   <si>
-    <t>Patient.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
     <t>urn:oid:1.2.250.1.213.1.4.2</t>
   </si>
   <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.value</t>
   </si>
   <si>
-    <t>Patient.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.period</t>
   </si>
   <si>
-    <t>Patient.identifier.period</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.assigner</t>
   </si>
   <si>
-    <t>Patient.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
     <t>Patient.identifier:NDP</t>
   </si>
   <si>
@@ -1549,9 +1596,6 @@
   </si>
   <si>
     <t>Patient.identifier:NDP.type</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1563,9 +1607,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
-  </si>
-  <si>
     <t>Patient.identifier:NDP.system</t>
   </si>
   <si>
@@ -1674,10 +1715,7 @@
     <t>INS-NIR</t>
   </si>
   <si>
-    <t>The patient's health national identifier INS coming from the INSi teleservice| Identifiant national de santé du patient INS provenant du téléservice INSi</t>
-  </si>
-  <si>
-    <t>patient's national identifier obtained by requesting the national patient identification service (CNAM) | Identifiant NIR du patient récupéré à partir de l'interrogation du service national d'identification des patients (CNAM)</t>
+    <t>INS-NIR - The patient health national identifier INS coming from the INSi teleservice | Numéro d'Inscription au Répertoire (NIR) du patient INS provenant du téléservice INSi de la CNAM.</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.id</t>
@@ -1687,9 +1725,6 @@
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.use</t>
-  </si>
-  <si>
-    <t>official</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.type</t>
@@ -1709,9 +1744,6 @@
     <t>Autorité d'affectation des INS-NIR</t>
   </si>
   <si>
-    <t>urn:oid:1.2.250.1.213.1.4.8</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-NIR.value</t>
   </si>
   <si>
@@ -1727,7 +1759,7 @@
     <t>INS-NIA</t>
   </si>
   <si>
-    <t>The temporary patient's health national identifier obtained by requesting the national patient identification service (CNAM)| Identifiant national temporaire de santé du patient obtenu par interrogation du téléservice INSi de la CNAM</t>
+    <t>INS-NIA - The temporary patient health national identifier obtained by requesting the national patient identification service (CNAM)| Identifiant national temporaire de santé du patient obtenu par interrogation du téléservice INSi de la CNAM.</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIA.id</t>
@@ -3026,7 +3058,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO185"/>
+  <dimension ref="A1:AO194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.5859375" customWidth="true" bestFit="true"/>
@@ -11360,7 +11392,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -11378,7 +11410,7 @@
         <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
@@ -11463,10 +11495,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11578,10 +11610,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11695,10 +11727,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11724,16 +11756,16 @@
         <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11743,7 +11775,7 @@
         <v>81</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>81</v>
@@ -11761,28 +11793,28 @@
         <v>264</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11797,7 +11829,7 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>81</v>
@@ -11814,10 +11846,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11840,13 +11872,13 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>442</v>
@@ -11916,7 +11948,7 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>81</v>
@@ -12419,7 +12451,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -12525,7 +12557,7 @@
         <v>489</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12640,7 +12672,7 @@
         <v>490</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12757,7 +12789,7 @@
         <v>491</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12783,16 +12815,16 @@
         <v>173</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12802,7 +12834,7 @@
         <v>81</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>433</v>
+        <v>492</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>81</v>
@@ -12820,28 +12852,28 @@
         <v>264</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12856,7 +12888,7 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>81</v>
@@ -12873,10 +12905,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12899,13 +12931,13 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="M85" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>442</v>
@@ -12938,9 +12970,11 @@
       <c r="X85" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y85" s="2"/>
+      <c r="Y85" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>495</v>
+        <v>446</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -12973,7 +13007,7 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>81</v>
@@ -12990,7 +13024,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>450</v>
@@ -13001,7 +13035,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>89</v>
@@ -13038,7 +13072,7 @@
         <v>81</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>456</v>
@@ -13109,7 +13143,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>461</v>
@@ -13226,7 +13260,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>470</v>
@@ -13343,7 +13377,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>477</v>
@@ -13460,13 +13494,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>81</v>
@@ -13491,10 +13525,10 @@
         <v>409</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>503</v>
+        <v>411</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
@@ -13579,10 +13613,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13694,10 +13728,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13811,10 +13845,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13840,16 +13874,16 @@
         <v>173</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -13859,7 +13893,7 @@
         <v>81</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>81</v>
@@ -13877,28 +13911,28 @@
         <v>264</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13913,7 +13947,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>81</v>
@@ -13930,10 +13964,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13956,13 +13990,13 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>442</v>
@@ -13978,7 +14012,7 @@
         <v>81</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>81</v>
@@ -14032,7 +14066,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>81</v>
@@ -14049,7 +14083,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>450</v>
@@ -14097,7 +14131,7 @@
         <v>81</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>456</v>
@@ -14168,7 +14202,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>461</v>
@@ -14285,7 +14319,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>470</v>
@@ -14402,7 +14436,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>477</v>
@@ -14519,13 +14553,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>81</v>
@@ -14535,7 +14569,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>81</v>
@@ -14550,10 +14584,10 @@
         <v>409</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>516</v>
+        <v>411</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -14638,10 +14672,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14753,10 +14787,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14870,10 +14904,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14899,16 +14933,16 @@
         <v>173</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14918,7 +14952,7 @@
         <v>81</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>433</v>
+        <v>519</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>81</v>
@@ -14936,28 +14970,28 @@
         <v>264</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z102" t="s" s="2">
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14972,7 +15006,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>81</v>
@@ -14992,7 +15026,7 @@
         <v>520</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15015,13 +15049,13 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>442</v>
@@ -15091,7 +15125,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>81</v>
@@ -15612,7 +15646,7 @@
         <v>528</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>529</v>
+        <v>411</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -15697,10 +15731,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15812,10 +15846,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15929,10 +15963,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15958,16 +15992,16 @@
         <v>173</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15977,7 +16011,7 @@
         <v>81</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>81</v>
@@ -15995,28 +16029,28 @@
         <v>264</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z111" t="s" s="2">
+      <c r="AA111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -16031,7 +16065,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>81</v>
@@ -16048,10 +16082,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16074,13 +16108,13 @@
         <v>90</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>442</v>
@@ -16096,7 +16130,7 @@
         <v>81</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>81</v>
@@ -16150,7 +16184,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>81</v>
@@ -16167,7 +16201,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>450</v>
@@ -16178,7 +16212,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>89</v>
@@ -16196,7 +16230,7 @@
         <v>133</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>537</v>
+        <v>451</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>452</v>
@@ -16215,7 +16249,7 @@
         <v>81</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>538</v>
+        <v>81</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>456</v>
@@ -16286,7 +16320,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>461</v>
@@ -16403,7 +16437,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>470</v>
@@ -16520,7 +16554,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>477</v>
@@ -16637,13 +16671,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
@@ -16668,10 +16702,10 @@
         <v>409</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>544</v>
+        <v>411</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
@@ -16756,10 +16790,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16871,10 +16905,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16988,10 +17022,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17017,16 +17051,16 @@
         <v>173</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -17036,7 +17070,7 @@
         <v>81</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>548</v>
+        <v>432</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>81</v>
@@ -17054,28 +17088,28 @@
         <v>264</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z120" t="s" s="2">
+      <c r="AA120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17090,7 +17124,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>81</v>
@@ -17107,10 +17141,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17133,13 +17167,13 @@
         <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>442</v>
@@ -17155,7 +17189,7 @@
         <v>81</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>81</v>
@@ -17209,7 +17243,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>81</v>
@@ -17226,7 +17260,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>450</v>
@@ -17255,7 +17289,7 @@
         <v>133</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>452</v>
@@ -17274,7 +17308,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>553</v>
+        <v>455</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>456</v>
@@ -17345,7 +17379,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>461</v>
@@ -17462,7 +17496,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>470</v>
@@ -17579,7 +17613,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>477</v>
@@ -17696,12 +17730,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="D126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17710,38 +17746,34 @@
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>558</v>
+        <v>409</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>562</v>
+        <v>412</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q126" t="s" s="2">
-        <v>563</v>
-      </c>
+      <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17785,13 +17817,13 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>557</v>
+        <v>408</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>101</v>
@@ -17800,16 +17832,16 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>564</v>
+        <v>415</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>109</v>
+        <v>416</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>565</v>
+        <v>417</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17817,10 +17849,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>566</v>
+        <v>423</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17828,10 +17860,10 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>81</v>
@@ -17840,23 +17872,19 @@
         <v>81</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>567</v>
+        <v>105</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>568</v>
+        <v>106</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17892,41 +17920,43 @@
         <v>81</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AC127" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>573</v>
+        <v>109</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -17934,16 +17964,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17959,23 +17987,21 @@
         <v>81</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>578</v>
+        <v>112</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>579</v>
+        <v>113</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>580</v>
+        <v>114</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
@@ -18011,19 +18037,19 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>566</v>
+        <v>119</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -18035,19 +18061,19 @@
         <v>101</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>573</v>
+        <v>103</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>81</v>
@@ -18055,10 +18081,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>582</v>
+        <v>427</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18075,22 +18101,26 @@
         <v>81</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>106</v>
+        <v>428</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
@@ -18099,7 +18129,7 @@
         <v>81</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>81</v>
+        <v>557</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>81</v>
@@ -18114,13 +18144,13 @@
         <v>81</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>81</v>
@@ -18138,7 +18168,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>108</v>
+        <v>435</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -18147,13 +18177,13 @@
         <v>89</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>109</v>
+        <v>436</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>81</v>
@@ -18162,7 +18192,7 @@
         <v>81</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>81</v>
@@ -18170,21 +18200,21 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>584</v>
+        <v>438</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -18193,21 +18223,23 @@
         <v>81</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>439</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>440</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
+        <v>441</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
@@ -18216,7 +18248,7 @@
         <v>81</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>81</v>
@@ -18231,46 +18263,46 @@
         <v>81</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>119</v>
+        <v>447</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>103</v>
+        <v>436</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>81</v>
@@ -18279,7 +18311,7 @@
         <v>81</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>81</v>
@@ -18287,10 +18319,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>586</v>
+        <v>450</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18298,7 +18330,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>89</v>
@@ -18307,25 +18339,25 @@
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>588</v>
+        <v>452</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>589</v>
+        <v>453</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>590</v>
+        <v>454</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -18335,10 +18367,10 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>507</v>
+        <v>562</v>
       </c>
       <c r="T131" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="U131" t="s" s="2">
         <v>81</v>
@@ -18350,13 +18382,13 @@
         <v>81</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>591</v>
+        <v>81</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>592</v>
+        <v>81</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>81</v>
@@ -18374,7 +18406,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>593</v>
+        <v>457</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18389,7 +18421,7 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>316</v>
+        <v>458</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>81</v>
@@ -18398,7 +18430,7 @@
         <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>594</v>
+        <v>459</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>81</v>
@@ -18406,10 +18438,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>595</v>
+        <v>563</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>596</v>
+        <v>461</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18417,7 +18449,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>89</v>
@@ -18435,17 +18467,15 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>597</v>
+        <v>462</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>598</v>
+        <v>463</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18457,7 +18487,7 @@
         <v>81</v>
       </c>
       <c r="T132" t="s" s="2">
-        <v>81</v>
+        <v>465</v>
       </c>
       <c r="U132" t="s" s="2">
         <v>81</v>
@@ -18493,7 +18523,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>600</v>
+        <v>466</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18508,7 +18538,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>336</v>
+        <v>467</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>81</v>
@@ -18517,7 +18547,7 @@
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>601</v>
+        <v>468</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18525,14 +18555,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>602</v>
+        <v>564</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>603</v>
+        <v>470</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>604</v>
+        <v>81</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18551,16 +18581,16 @@
         <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>605</v>
+        <v>471</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>606</v>
+        <v>472</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>607</v>
+        <v>396</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18610,7 +18640,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>608</v>
+        <v>473</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18622,10 +18652,10 @@
         <v>101</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>102</v>
+        <v>400</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>609</v>
+        <v>474</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>81</v>
@@ -18634,7 +18664,7 @@
         <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>610</v>
+        <v>475</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>81</v>
@@ -18642,21 +18672,21 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>612</v>
+        <v>477</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>613</v>
+        <v>81</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>81</v>
@@ -18668,16 +18698,16 @@
         <v>90</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>105</v>
+        <v>478</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>614</v>
+        <v>479</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>615</v>
+        <v>480</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>616</v>
+        <v>481</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18727,22 +18757,22 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>617</v>
+        <v>482</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>102</v>
+        <v>483</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>618</v>
+        <v>484</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>81</v>
@@ -18751,7 +18781,7 @@
         <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>619</v>
+        <v>485</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>81</v>
@@ -18759,10 +18789,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>620</v>
+        <v>566</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>621</v>
+        <v>566</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18773,34 +18803,38 @@
         <v>79</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J135" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>105</v>
+        <v>567</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>622</v>
+        <v>568</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>623</v>
+        <v>569</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O135" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q135" s="2"/>
+      <c r="Q135" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="R135" t="s" s="2">
         <v>81</v>
       </c>
@@ -18844,13 +18878,13 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>624</v>
+        <v>566</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>101</v>
@@ -18859,16 +18893,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>625</v>
+        <v>573</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>81</v>
+        <v>574</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>626</v>
+        <v>81</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>81</v>
@@ -18876,10 +18910,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>627</v>
+        <v>575</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>628</v>
+        <v>575</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18887,7 +18921,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>80</v>
@@ -18902,18 +18936,20 @@
         <v>90</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>105</v>
+        <v>576</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>629</v>
+        <v>577</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>630</v>
+        <v>578</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O136" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
       </c>
@@ -18949,19 +18985,17 @@
         <v>81</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>631</v>
+        <v>575</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18976,16 +19010,16 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>632</v>
+        <v>582</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>633</v>
+        <v>584</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>81</v>
@@ -18993,12 +19027,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>634</v>
+        <v>585</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
       </c>
@@ -19007,7 +19043,7 @@
         <v>79</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>81</v>
@@ -19019,19 +19055,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>393</v>
+        <v>587</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>396</v>
+        <v>579</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>638</v>
+        <v>580</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -19080,31 +19116,31 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>639</v>
+        <v>575</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>401</v>
+        <v>582</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>640</v>
+        <v>584</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>81</v>
@@ -19112,20 +19148,18 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>641</v>
+        <v>590</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>89</v>
@@ -19137,23 +19171,19 @@
         <v>81</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>578</v>
+        <v>105</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>643</v>
+        <v>106</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>81</v>
       </c>
@@ -19201,31 +19231,31 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>573</v>
+        <v>109</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>81</v>
@@ -19233,21 +19263,21 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>645</v>
+        <v>592</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>81</v>
@@ -19259,15 +19289,17 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -19304,34 +19336,34 @@
         <v>81</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>81</v>
@@ -19348,10 +19380,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>594</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19362,28 +19394,32 @@
         <v>89</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>198</v>
+        <v>596</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19392,7 +19428,7 @@
         <v>81</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>81</v>
@@ -19407,46 +19443,46 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>81</v>
+        <v>600</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>81</v>
+        <v>601</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>119</v>
+        <v>602</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>81</v>
@@ -19455,7 +19491,7 @@
         <v>81</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>81</v>
+        <v>603</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -19463,20 +19499,18 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>647</v>
+        <v>604</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G141" t="s" s="2">
         <v>89</v>
@@ -19488,19 +19522,23 @@
         <v>81</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>649</v>
+        <v>105</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>650</v>
+        <v>606</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19548,22 +19586,22 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>119</v>
+        <v>609</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>81</v>
@@ -19572,7 +19610,7 @@
         <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>81</v>
@@ -19580,18 +19618,18 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>81</v>
+        <v>613</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>89</v>
@@ -19600,26 +19638,24 @@
         <v>81</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>588</v>
+        <v>615</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19628,7 +19664,7 @@
         <v>81</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>81</v>
@@ -19643,13 +19679,13 @@
         <v>81</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>591</v>
+        <v>81</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>592</v>
+        <v>81</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>81</v>
@@ -19667,7 +19703,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19682,7 +19718,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>316</v>
+        <v>618</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>81</v>
@@ -19691,7 +19727,7 @@
         <v>81</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>81</v>
@@ -19699,21 +19735,21 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>653</v>
+        <v>620</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>81</v>
+        <v>622</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>
@@ -19728,17 +19764,15 @@
         <v>105</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>81</v>
       </c>
@@ -19786,13 +19820,13 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>101</v>
@@ -19801,7 +19835,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>336</v>
+        <v>627</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>81</v>
@@ -19810,7 +19844,7 @@
         <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>601</v>
+        <v>628</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>81</v>
@@ -19818,21 +19852,21 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>654</v>
+        <v>629</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>604</v>
+        <v>81</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>81</v>
@@ -19847,13 +19881,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>607</v>
+        <v>342</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19903,13 +19937,13 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>101</v>
@@ -19918,7 +19952,7 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>81</v>
@@ -19927,7 +19961,7 @@
         <v>81</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>81</v>
@@ -19935,21 +19969,21 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>655</v>
+        <v>636</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>613</v>
+        <v>81</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>81</v>
@@ -19964,13 +19998,13 @@
         <v>105</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>616</v>
+        <v>342</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20020,7 +20054,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20035,7 +20069,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>81</v>
@@ -20044,7 +20078,7 @@
         <v>81</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>81</v>
@@ -20052,10 +20086,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20066,7 +20100,7 @@
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>81</v>
@@ -20078,18 +20112,20 @@
         <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>647</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>81</v>
       </c>
@@ -20137,22 +20173,22 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>400</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>625</v>
+        <v>401</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>81</v>
@@ -20161,7 +20197,7 @@
         <v>81</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>81</v>
@@ -20169,21 +20205,23 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C147" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="D147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>81</v>
@@ -20195,18 +20233,20 @@
         <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>105</v>
+        <v>587</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O147" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>81</v>
       </c>
@@ -20254,7 +20294,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>631</v>
+        <v>575</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20269,16 +20309,16 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>632</v>
+        <v>582</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>633</v>
+        <v>584</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>81</v>
@@ -20286,10 +20326,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>635</v>
+        <v>591</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20309,23 +20349,19 @@
         <v>81</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>636</v>
+        <v>106</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>81</v>
       </c>
@@ -20373,7 +20409,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>639</v>
+        <v>108</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20382,13 +20418,13 @@
         <v>89</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>401</v>
+        <v>109</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>81</v>
@@ -20397,7 +20433,7 @@
         <v>81</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>640</v>
+        <v>81</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>81</v>
@@ -20405,10 +20441,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>660</v>
+        <v>593</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20416,7 +20452,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>80</v>
@@ -20431,20 +20467,16 @@
         <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>661</v>
+        <v>112</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>662</v>
+        <v>198</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>81</v>
       </c>
@@ -20480,19 +20512,19 @@
         <v>81</v>
       </c>
       <c r="AB149" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>660</v>
+        <v>119</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20504,10 +20536,10 @@
         <v>101</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>666</v>
+        <v>120</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>667</v>
+        <v>81</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>81</v>
@@ -20516,7 +20548,7 @@
         <v>81</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>668</v>
+        <v>81</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>81</v>
@@ -20524,12 +20556,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C150" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="D150" t="s" s="2">
         <v>81</v>
       </c>
@@ -20547,23 +20581,19 @@
         <v>81</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>173</v>
+        <v>658</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>673</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>81</v>
       </c>
@@ -20587,11 +20617,13 @@
         <v>81</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="Y150" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z150" t="s" s="2">
-        <v>674</v>
+        <v>81</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>81</v>
@@ -20609,31 +20641,31 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>669</v>
+        <v>119</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>675</v>
+        <v>81</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>676</v>
+        <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>677</v>
+        <v>81</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>81</v>
@@ -20641,10 +20673,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>678</v>
+        <v>595</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20661,25 +20693,25 @@
         <v>81</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J151" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>679</v>
+        <v>596</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>679</v>
+        <v>597</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>680</v>
+        <v>598</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>681</v>
+        <v>599</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>81</v>
@@ -20689,7 +20721,7 @@
         <v>81</v>
       </c>
       <c r="S151" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="T151" t="s" s="2">
         <v>81</v>
@@ -20704,13 +20736,13 @@
         <v>81</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>81</v>
+        <v>600</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>81</v>
+        <v>601</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>81</v>
@@ -20728,7 +20760,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>678</v>
+        <v>602</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20743,27 +20775,27 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>682</v>
+        <v>316</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>683</v>
+        <v>81</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>684</v>
+        <v>603</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>685</v>
+        <v>81</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>686</v>
+        <v>605</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20780,25 +20812,25 @@
         <v>81</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J152" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>687</v>
+        <v>105</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>688</v>
+        <v>606</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>689</v>
+        <v>607</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>690</v>
+        <v>608</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>691</v>
+        <v>333</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -20847,7 +20879,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>686</v>
+        <v>609</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20862,16 +20894,16 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>692</v>
+        <v>336</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>693</v>
+        <v>610</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>81</v>
@@ -20879,21 +20911,21 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>694</v>
+        <v>663</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>694</v>
+        <v>612</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>81</v>
+        <v>613</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>81</v>
@@ -20902,23 +20934,21 @@
         <v>81</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>291</v>
+        <v>105</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>292</v>
+        <v>614</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>293</v>
+        <v>615</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>81</v>
       </c>
@@ -20966,13 +20996,13 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>694</v>
+        <v>617</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>101</v>
@@ -20981,7 +21011,7 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>295</v>
+        <v>618</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>81</v>
@@ -20990,7 +21020,7 @@
         <v>81</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>296</v>
+        <v>619</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>81</v>
@@ -20998,18 +21028,18 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>696</v>
+        <v>664</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>696</v>
+        <v>621</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>81</v>
+        <v>622</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>89</v>
@@ -21021,23 +21051,21 @@
         <v>81</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>440</v>
+        <v>105</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>697</v>
+        <v>665</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>698</v>
+        <v>624</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>81</v>
       </c>
@@ -21061,11 +21089,13 @@
         <v>81</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y154" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z154" t="s" s="2">
-        <v>701</v>
+        <v>81</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>81</v>
@@ -21083,13 +21113,13 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>696</v>
+        <v>626</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>101</v>
@@ -21098,16 +21128,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>702</v>
+        <v>627</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>703</v>
+        <v>81</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>704</v>
+        <v>628</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21115,10 +21145,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>705</v>
+        <v>666</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>705</v>
+        <v>630</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21129,7 +21159,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>81</v>
@@ -21138,23 +21168,21 @@
         <v>81</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>706</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>707</v>
+        <v>631</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>708</v>
+        <v>632</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>710</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>81</v>
       </c>
@@ -21202,13 +21230,13 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>705</v>
+        <v>633</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>101</v>
@@ -21217,16 +21245,16 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>711</v>
+        <v>634</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>712</v>
+        <v>635</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>81</v>
@@ -21234,10 +21262,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>713</v>
+        <v>667</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>713</v>
+        <v>637</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21257,23 +21285,21 @@
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>714</v>
+        <v>105</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>715</v>
+        <v>638</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>716</v>
+        <v>639</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>81</v>
       </c>
@@ -21321,7 +21347,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>713</v>
+        <v>640</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21333,19 +21359,19 @@
         <v>101</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>719</v>
+        <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>720</v>
+        <v>641</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>721</v>
+        <v>642</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>81</v>
@@ -21353,10 +21379,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>722</v>
+        <v>668</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>722</v>
+        <v>644</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21367,7 +21393,7 @@
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>81</v>
@@ -21376,22 +21402,22 @@
         <v>81</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>723</v>
+        <v>393</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>724</v>
+        <v>645</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>725</v>
+        <v>646</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>726</v>
+        <v>396</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>727</v>
+        <v>647</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21440,31 +21466,31 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>722</v>
+        <v>648</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>728</v>
+        <v>400</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>729</v>
+        <v>401</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>81</v>
+        <v>649</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>81</v>
@@ -21472,10 +21498,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>730</v>
+        <v>669</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>730</v>
+        <v>669</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21486,7 +21512,7 @@
         <v>79</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>81</v>
@@ -21498,16 +21524,20 @@
         <v>81</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>105</v>
+        <v>670</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>106</v>
+        <v>671</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N158" s="2"/>
-      <c r="O158" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>674</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
       </c>
@@ -21555,22 +21585,22 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>108</v>
+        <v>669</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>81</v>
+        <v>675</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>109</v>
+        <v>676</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>81</v>
@@ -21579,7 +21609,7 @@
         <v>81</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>81</v>
+        <v>677</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>81</v>
@@ -21587,21 +21617,21 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>731</v>
+        <v>678</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>731</v>
+        <v>678</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>81</v>
@@ -21610,21 +21640,23 @@
         <v>81</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>113</v>
+        <v>679</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>114</v>
+        <v>680</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
       </c>
@@ -21648,55 +21680,53 @@
         <v>81</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>81</v>
+        <v>683</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>119</v>
+        <v>678</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>103</v>
+        <v>684</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>81</v>
+        <v>685</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>81</v>
+        <v>686</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>81</v>
@@ -21704,20 +21734,18 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>732</v>
+        <v>687</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>733</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21729,19 +21757,23 @@
         <v>81</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>734</v>
+        <v>241</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>735</v>
+        <v>688</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>690</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>81</v>
       </c>
@@ -21789,46 +21821,44 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>119</v>
+        <v>687</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>81</v>
+        <v>691</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>81</v>
+        <v>692</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>81</v>
+        <v>693</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>81</v>
+        <v>694</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>737</v>
+        <v>695</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>738</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
         <v>81</v>
       </c>
@@ -21843,22 +21873,26 @@
         <v>81</v>
       </c>
       <c r="I161" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>739</v>
+        <v>696</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>740</v>
+        <v>697</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N161" s="2"/>
-      <c r="O161" s="2"/>
+        <v>698</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>700</v>
+      </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
       </c>
@@ -21906,31 +21940,31 @@
         <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>119</v>
+        <v>695</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>81</v>
+        <v>701</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>81</v>
+        <v>702</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>81</v>
@@ -21938,14 +21972,14 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>742</v>
+        <v>703</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>742</v>
+        <v>703</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>743</v>
+        <v>81</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21958,25 +21992,25 @@
         <v>81</v>
       </c>
       <c r="I162" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>112</v>
+        <v>291</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>744</v>
+        <v>292</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>745</v>
+        <v>293</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>115</v>
+        <v>294</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>406</v>
+        <v>704</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
@@ -22025,7 +22059,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>746</v>
+        <v>703</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22037,10 +22071,10 @@
         <v>101</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>103</v>
+        <v>295</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>81</v>
@@ -22049,7 +22083,7 @@
         <v>81</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>81</v>
@@ -22057,10 +22091,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>747</v>
+        <v>705</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>747</v>
+        <v>705</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22068,7 +22102,7 @@
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
         <v>89</v>
@@ -22083,19 +22117,19 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>748</v>
+        <v>706</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>749</v>
+        <v>707</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>750</v>
+        <v>709</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22122,33 +22156,33 @@
       <c r="X163" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y163" t="s" s="2">
-        <v>751</v>
-      </c>
+      <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>752</v>
+        <v>710</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="AC163" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>747</v>
+        <v>705</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>101</v>
@@ -22157,16 +22191,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>754</v>
+        <v>711</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>109</v>
+        <v>712</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>755</v>
+        <v>713</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
@@ -22174,14 +22208,12 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>756</v>
+        <v>714</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>757</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>81</v>
       </c>
@@ -22202,19 +22234,19 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>440</v>
+        <v>715</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>758</v>
+        <v>716</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>749</v>
+        <v>717</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>699</v>
+        <v>718</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22239,11 +22271,13 @@
         <v>81</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>759</v>
+        <v>81</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>81</v>
@@ -22261,13 +22295,13 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>747</v>
+        <v>714</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>101</v>
@@ -22276,7 +22310,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>754</v>
+        <v>720</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>109</v>
@@ -22285,7 +22319,7 @@
         <v>81</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>755</v>
+        <v>721</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
@@ -22293,14 +22327,12 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>760</v>
+        <v>722</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>761</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>81</v>
       </c>
@@ -22309,7 +22341,7 @@
         <v>79</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>81</v>
@@ -22321,19 +22353,19 @@
         <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>440</v>
+        <v>723</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>762</v>
+        <v>724</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>749</v>
+        <v>725</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>750</v>
+        <v>727</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22358,11 +22390,13 @@
         <v>81</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y165" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z165" t="s" s="2">
-        <v>763</v>
+        <v>81</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -22380,7 +22414,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>747</v>
+        <v>722</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22392,10 +22426,10 @@
         <v>101</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>102</v>
+        <v>728</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>754</v>
+        <v>729</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>109</v>
@@ -22404,7 +22438,7 @@
         <v>81</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>81</v>
@@ -22412,10 +22446,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22426,7 +22460,7 @@
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>81</v>
@@ -22438,19 +22472,19 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>567</v>
+        <v>732</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>765</v>
+        <v>733</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>766</v>
+        <v>734</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>767</v>
+        <v>735</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>768</v>
+        <v>736</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22499,31 +22533,31 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>102</v>
+        <v>737</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>769</v>
+        <v>738</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>770</v>
+        <v>81</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>81</v>
@@ -22531,10 +22565,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>771</v>
+        <v>739</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>771</v>
+        <v>739</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22545,7 +22579,7 @@
         <v>79</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>81</v>
@@ -22557,20 +22591,16 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>661</v>
+        <v>105</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>662</v>
+        <v>106</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>81</v>
       </c>
@@ -22618,22 +22648,22 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>771</v>
+        <v>108</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>666</v>
+        <v>81</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>667</v>
+        <v>109</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>81</v>
@@ -22642,7 +22672,7 @@
         <v>81</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>668</v>
+        <v>81</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>81</v>
@@ -22650,21 +22680,21 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>773</v>
+        <v>740</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>773</v>
+        <v>740</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>81</v>
@@ -22676,20 +22706,18 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>774</v>
+        <v>112</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>775</v>
+        <v>113</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>776</v>
+        <v>114</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>777</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>81</v>
       </c>
@@ -22725,43 +22753,43 @@
         <v>81</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>773</v>
+        <v>119</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>778</v>
+        <v>103</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>779</v>
+        <v>81</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>81</v>
@@ -22769,12 +22797,14 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>780</v>
+        <v>741</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="C169" s="2"/>
+        <v>740</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="D169" t="s" s="2">
         <v>81</v>
       </c>
@@ -22795,20 +22825,16 @@
         <v>81</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>173</v>
+        <v>743</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>781</v>
+        <v>744</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>783</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>81</v>
       </c>
@@ -22832,13 +22858,13 @@
         <v>81</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>784</v>
+        <v>81</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>785</v>
+        <v>81</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -22856,31 +22882,31 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>780</v>
+        <v>119</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>675</v>
+        <v>81</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>786</v>
+        <v>81</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22888,12 +22914,14 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>787</v>
+        <v>746</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C170" s="2"/>
+        <v>740</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>747</v>
+      </c>
       <c r="D170" t="s" s="2">
         <v>81</v>
       </c>
@@ -22914,20 +22942,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>478</v>
+        <v>748</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>788</v>
+        <v>749</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>791</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>81</v>
       </c>
@@ -22975,31 +22999,31 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>787</v>
+        <v>119</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>792</v>
+        <v>101</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>483</v>
+        <v>120</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>793</v>
+        <v>81</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>794</v>
+        <v>81</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>81</v>
@@ -23007,44 +23031,46 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>795</v>
+        <v>751</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>795</v>
+        <v>751</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>81</v>
+        <v>752</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I171" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>393</v>
+        <v>112</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>796</v>
+        <v>753</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>797</v>
+        <v>754</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>81</v>
       </c>
@@ -23092,31 +23118,31 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>795</v>
+        <v>755</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>798</v>
+        <v>103</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>799</v>
+        <v>81</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>81</v>
@@ -23124,10 +23150,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>800</v>
+        <v>756</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>800</v>
+        <v>756</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23135,10 +23161,10 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>81</v>
@@ -23150,19 +23176,19 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>723</v>
+        <v>439</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>801</v>
+        <v>757</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>802</v>
+        <v>758</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>803</v>
+        <v>708</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>804</v>
+        <v>759</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -23187,31 +23213,29 @@
         <v>81</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>81</v>
+        <v>760</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>81</v>
+        <v>761</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>762</v>
+      </c>
+      <c r="AC172" s="2"/>
       <c r="AD172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>800</v>
+        <v>756</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23226,16 +23250,16 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>805</v>
+        <v>763</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>806</v>
+        <v>109</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>81</v>
+        <v>764</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>81</v>
@@ -23243,12 +23267,14 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="C173" s="2"/>
+        <v>756</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>766</v>
+      </c>
       <c r="D173" t="s" s="2">
         <v>81</v>
       </c>
@@ -23269,16 +23295,20 @@
         <v>81</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>105</v>
+        <v>439</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>106</v>
+        <v>767</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>758</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>759</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>81</v>
       </c>
@@ -23302,13 +23332,11 @@
         <v>81</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>81</v>
+        <v>768</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>81</v>
@@ -23326,31 +23354,31 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>108</v>
+        <v>756</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AL173" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AL173" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>81</v>
+        <v>764</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>81</v>
@@ -23358,21 +23386,23 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>808</v>
+        <v>769</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="C174" s="2"/>
+        <v>756</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>770</v>
+      </c>
       <c r="D174" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>81</v>
@@ -23384,18 +23414,20 @@
         <v>81</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>112</v>
+        <v>439</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>113</v>
+        <v>771</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>114</v>
+        <v>758</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O174" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>759</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>81</v>
       </c>
@@ -23419,31 +23451,29 @@
         <v>81</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>81</v>
+        <v>772</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>119</v>
+        <v>756</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23455,19 +23485,19 @@
         <v>101</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>103</v>
+        <v>763</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>81</v>
+        <v>764</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>81</v>
@@ -23475,45 +23505,45 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>809</v>
+        <v>773</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>809</v>
+        <v>773</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>743</v>
+        <v>81</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>112</v>
+        <v>576</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>744</v>
+        <v>774</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>745</v>
+        <v>775</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>115</v>
+        <v>776</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>406</v>
+        <v>777</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>81</v>
@@ -23562,22 +23592,22 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>103</v>
+        <v>778</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>81</v>
@@ -23586,7 +23616,7 @@
         <v>81</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>81</v>
+        <v>779</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>81</v>
@@ -23594,10 +23624,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23605,10 +23635,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>81</v>
@@ -23620,19 +23650,19 @@
         <v>81</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>440</v>
+        <v>670</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>811</v>
+        <v>671</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>812</v>
+        <v>672</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>813</v>
+        <v>781</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>814</v>
+        <v>674</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23657,13 +23687,13 @@
         <v>81</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>81</v>
@@ -23681,31 +23711,31 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>102</v>
+        <v>675</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>815</v>
+        <v>676</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>816</v>
+        <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>817</v>
+        <v>677</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>81</v>
@@ -23713,10 +23743,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>818</v>
+        <v>782</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>818</v>
+        <v>782</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23739,19 +23769,19 @@
         <v>81</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>558</v>
+        <v>783</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>819</v>
+        <v>784</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>820</v>
+        <v>785</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>821</v>
+        <v>294</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>822</v>
+        <v>786</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>81</v>
@@ -23800,7 +23830,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>818</v>
+        <v>782</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23815,16 +23845,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>823</v>
+        <v>787</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>824</v>
+        <v>109</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>825</v>
+        <v>788</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23832,21 +23862,21 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>826</v>
+        <v>789</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>826</v>
+        <v>789</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>827</v>
+        <v>81</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>81</v>
@@ -23858,18 +23888,20 @@
         <v>81</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>828</v>
+        <v>173</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>829</v>
+        <v>790</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>830</v>
+        <v>791</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="O178" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>792</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>81</v>
       </c>
@@ -23893,13 +23925,13 @@
         <v>81</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>81</v>
+        <v>793</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>81</v>
+        <v>794</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>81</v>
@@ -23917,22 +23949,22 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>826</v>
+        <v>789</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>483</v>
+        <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>832</v>
+        <v>684</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>109</v>
@@ -23941,7 +23973,7 @@
         <v>81</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>833</v>
+        <v>795</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>81</v>
@@ -23949,10 +23981,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>834</v>
+        <v>796</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>834</v>
+        <v>796</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23972,22 +24004,22 @@
         <v>81</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>835</v>
+        <v>478</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>836</v>
+        <v>797</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>837</v>
+        <v>798</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>838</v>
+        <v>799</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>839</v>
+        <v>800</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
@@ -24036,7 +24068,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>834</v>
+        <v>796</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24045,22 +24077,22 @@
         <v>89</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>101</v>
+        <v>801</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>483</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>840</v>
+        <v>109</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>81</v>
+        <v>803</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>81</v>
@@ -24068,10 +24100,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>841</v>
+        <v>804</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>841</v>
+        <v>804</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24082,32 +24114,30 @@
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I180" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>723</v>
+        <v>393</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>842</v>
+        <v>805</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>843</v>
+        <v>806</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>845</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>81</v>
       </c>
@@ -24155,22 +24185,22 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>841</v>
+        <v>804</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>102</v>
+        <v>400</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>846</v>
+        <v>807</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>109</v>
@@ -24179,7 +24209,7 @@
         <v>81</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>81</v>
+        <v>808</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>81</v>
@@ -24187,10 +24217,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>847</v>
+        <v>809</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>847</v>
+        <v>809</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24201,7 +24231,7 @@
         <v>79</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>81</v>
@@ -24213,16 +24243,20 @@
         <v>81</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>105</v>
+        <v>732</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>106</v>
+        <v>810</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N181" s="2"/>
-      <c r="O181" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>813</v>
+      </c>
       <c r="P181" t="s" s="2">
         <v>81</v>
       </c>
@@ -24270,25 +24304,25 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>108</v>
+        <v>809</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>109</v>
+        <v>814</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>81</v>
+        <v>815</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>81</v>
@@ -24302,21 +24336,21 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>848</v>
+        <v>816</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>848</v>
+        <v>816</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>81</v>
@@ -24328,17 +24362,15 @@
         <v>81</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>81</v>
@@ -24375,34 +24407,34 @@
         <v>81</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>81</v>
@@ -24419,14 +24451,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>849</v>
+        <v>817</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>849</v>
+        <v>817</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>743</v>
+        <v>111</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24439,26 +24471,24 @@
         <v>81</v>
       </c>
       <c r="I183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K183" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>744</v>
+        <v>113</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>745</v>
+        <v>114</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O183" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>81</v>
       </c>
@@ -24494,19 +24524,19 @@
         <v>81</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>746</v>
+        <v>119</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24538,44 +24568,46 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>850</v>
+        <v>818</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>850</v>
+        <v>818</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>81</v>
+        <v>752</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I184" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J184" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>851</v>
+        <v>112</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>852</v>
+        <v>753</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>853</v>
+        <v>754</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="O184" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
       </c>
@@ -24623,31 +24655,31 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>850</v>
+        <v>755</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>483</v>
+        <v>120</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>415</v>
+        <v>103</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>855</v>
+        <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>81</v>
@@ -24655,10 +24687,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>856</v>
+        <v>819</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>856</v>
+        <v>819</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24678,21 +24710,23 @@
         <v>81</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>173</v>
+        <v>439</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>857</v>
+        <v>820</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>858</v>
+        <v>821</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>822</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>823</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24716,13 +24750,13 @@
         <v>81</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>858</v>
+        <v>178</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>859</v>
+        <v>179</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>81</v>
@@ -24740,7 +24774,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>856</v>
+        <v>819</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24755,18 +24789,1077 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AL185" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="AM185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN185" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="AO185" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="P186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q186" s="2"/>
+      <c r="R186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK186" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="AL186" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AM186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN186" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="AO186" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="O187" s="2"/>
+      <c r="P187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AK187" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="AL187" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN187" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="AO187" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G188" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J188" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K188" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="L188" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="O188" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="P188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q188" s="2"/>
+      <c r="R188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF188" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="AG188" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH188" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI188" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ188" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AK188" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AL188" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AM188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO188" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="C189" s="2"/>
+      <c r="D189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G189" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I189" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J189" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K189" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="P189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q189" s="2"/>
+      <c r="R189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF189" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="AG189" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH189" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI189" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ189" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK189" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="AL189" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO189" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="C190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N190" s="2"/>
+      <c r="O190" s="2"/>
+      <c r="P190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q190" s="2"/>
+      <c r="R190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK190" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AL190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO190" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="C191" s="2"/>
+      <c r="D191" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G191" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K191" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L191" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O191" s="2"/>
+      <c r="P191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q191" s="2"/>
+      <c r="R191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF191" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK191" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO191" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="P192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q192" s="2"/>
+      <c r="R192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK192" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO192" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K193" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="AL185" t="s" s="2">
+      <c r="L193" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="O193" s="2"/>
+      <c r="P193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q193" s="2"/>
+      <c r="R193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AK193" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL193" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AM185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO185" t="s" s="2">
+      <c r="AM193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN193" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="AO193" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O194" s="2"/>
+      <c r="P194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK194" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="AL194" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO194" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:02:40+00:00</t>
+    <t>2024-02-26T11:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T10:55:37+00:00</t>
+    <t>2024-03-11T09:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T09:42:54+00:00</t>
+    <t>2024-03-11T10:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:34:02+00:00</t>
+    <t>2024-03-20T14:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:49:36+00:00</t>
+    <t>2024-03-21T08:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
